--- a/02_kdv_tevkifat_hesaplama_ve_beyan_tablosu.xlsx
+++ b/02_kdv_tevkifat_hesaplama_ve_beyan_tablosu.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KDV Tevkifat Listesi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KDV Tevkifat Listesi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİB Tevkifat Kodları" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0/10"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;TL&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,27 +32,33 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00E2E8F0"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <color rgb="000F172A"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="000F172A"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +69,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E3A8A"/>
         <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+        <bgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00334155"/>
+        <bgColor rgb="00334155"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,24 +124,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,83 +513,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KDV TEVKİFAT HESAPLAMA VE KDV-2 BEYAN TABLOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>GİB E-FATURA &amp; E-ARŞİV KDV TEVKİFAT HESAPLAMA VE BEYAN ÇİZELGESİ</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GİB 601-626 Tevkifat Kodları, KDV-2 Alıcı Beyanı ve Fatura Eşleştirme Motoru</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Sıra</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Fatura No</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Alıcı / Mükellef Ünvanı</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Hizmet / İş Türü</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Alıcı / Mükellef Unvanı</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>GİB Kodu</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Tevkifat Kapsamı / İş Türü</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Tevkifat Oranı</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Matrah (TL)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Toplam KDV (%20)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Tevkif Edilen KDV (2 Nolu KDV)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Hesaplanan KDV (%20)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Tevkif Edilen KDV</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Tahsil Edilen KDV</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Fatura Toplamı</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -573,42 +635,51 @@
           <t>FTR2026001</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Anadolu İnşaat A.Ş.</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Anadolu Yapı Yatırım A.Ş.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Yapım İşleri</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Yapım İşleri ve Mimarlık-Mühendislik</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H4" s="6">
-        <f>G4*0.20</f>
-        <v/>
-      </c>
-      <c r="I4" s="6">
-        <f>H4*F4</f>
-        <v/>
-      </c>
-      <c r="J4" s="6">
-        <f>H4-I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="H4" s="7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I4" s="7">
+        <f>H4*0.20</f>
+        <v/>
+      </c>
+      <c r="J4" s="7">
+        <f>I4*G4</f>
+        <v/>
+      </c>
+      <c r="K4" s="7">
+        <f>I4-J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="7">
+        <f>H4+K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -616,200 +687,881 @@
           <t>FTR2026002</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Marmara Lojistik Ltd.</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Marmara Uluslararası Lojistik Ltd.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Servis Taşımacılığı</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Yük Taşımacılığı Hizmeti</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I5" s="7">
+        <f>H5*0.20</f>
+        <v/>
+      </c>
+      <c r="J5" s="7">
+        <f>I5*G5</f>
+        <v/>
+      </c>
+      <c r="K5" s="7">
+        <f>I5-J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="7">
+        <f>H5+K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>FTR2026003</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Boğaziçi Denetim ve Danışmanlık A.Ş.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Danışmanlık ve Denetim Hizmetleri</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I6" s="7">
+        <f>H6*0.20</f>
+        <v/>
+      </c>
+      <c r="J6" s="7">
+        <f>I6*G6</f>
+        <v/>
+      </c>
+      <c r="K6" s="7">
+        <f>I6-J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="7">
+        <f>H6+K6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>FTR2026004</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Ege Çelik Endüstrisi Sanayi Ltd.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Demir-Çelik Ürünlerinin Teslimi</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I7" s="7">
+        <f>H7*0.20</f>
+        <v/>
+      </c>
+      <c r="J7" s="7">
+        <f>I7*G7</f>
+        <v/>
+      </c>
+      <c r="K7" s="7">
+        <f>I7-J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="7">
+        <f>H7+K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>FTR2026005</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Akdeniz Tekstil Konfeksiyon A.Ş.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Fason Tekstil ve Konfeksiyon İşleri</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I8" s="7">
+        <f>H8*0.20</f>
+        <v/>
+      </c>
+      <c r="J8" s="7">
+        <f>I8*G8</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>I8-J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>H8+K8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>FTR2026006</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Yıldız Özel Güvenlik ve Koruma Ltd.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Özel Güvenlik Hizmeti</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I9" s="7">
+        <f>H9*0.20</f>
+        <v/>
+      </c>
+      <c r="J9" s="7">
+        <f>I9*G9</f>
+        <v/>
+      </c>
+      <c r="K9" s="7">
+        <f>I9-J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="7">
+        <f>H9+K9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>GENEL TOPLAMLAR</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="9">
+        <f>SUM(H4:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>SUM(I4:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f>SUM(J4:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="9">
+        <f>SUM(K4:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="9">
+        <f>SUM(L4:L9)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="63" customWidth="1" min="1" max="1"/>
+    <col width="97" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="92" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GELİR İDARESİ BAŞKANLIĞI (GİB) KDV TEVKİFAT KODLARI LİSTESİ</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>GİB Kodu</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>İşlem Türü / Hizmet Adı</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Tevkifat Oranı (Metin)</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Tevkifat Oranı (Ondalık)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Açıklama &amp; Yasal Dayanak</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Yapım İşleri ile Bu İşlerle Birlikte İfa Edilen Mühendislik-Mimarlık ve Etüt-Proje Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Belirlenmiş alıcılara veya KDV mükelleflerine karşı ifa edilen yapım taahhüt işleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Etüt, Plan-Proje, Danışmanlık, Denetim ve Benzeri Hizmetler</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Piyasa araştırması, teknik müşavirlik, mali danışmanlık ve denetim hizmetleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Makine, Teçhizat, Demirbaş ve Taşıtlara Ait Tadil, Bakım ve Onarım Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>İşletmeye dahil aktif kıymetlerin bakım ve onarım işleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Yemek Servis ve Organizasyon Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H5" s="6">
-        <f>G5*0.20</f>
-        <v/>
-      </c>
-      <c r="I5" s="6">
-        <f>H5*F5</f>
-        <v/>
-      </c>
-      <c r="J5" s="6">
-        <f>H5-I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>FTR2026003</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Boğaziçi Teknoloji A.Ş.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Danışmanlık / Denetim</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Toplu yemek, tabldot servisi ve catering organizasyonları.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>İşgücü Temin Hizmetleri (Özel Güvenlik Dahil)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Hizmet akdiyle bağlı personelin başka bir firmanın sevk ve idaresine verilmesi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Özel Güvenlik Hizmeti</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>5188 sayılı Kanun kapsamında güvenlik şirketlerince sağlanan koruma hizmetleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Yapı Denetim Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Yapı denetim kuruluşları tarafından arsa sahibi veya müteahhide verilen denetim hizmeti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Fason Olarak Yaptırılan Tekstil ve Konfeksiyon İşleri</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Kumaş, deri ve konfeksiyon fason dikim, kesim, boyama ve ütüleme işleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Turistik Mağazalara Verilen Müşteri Bulma / Götürme Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Rehber ve acenteler tarafından mağazalara müşteri yönlendirilmesi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Spor Kulüplerinin Yayın, Reklâm ve İsim Hakkı Gelirleri</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Profesyonel kulüplerin sponsorluk, forma reklamı ve isim hakkı devirleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Temizlik, Çevre ve Bahçe Bakım Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Bina içi/dışı genel temizlik, dezenfeksiyon ve çevre düzenleme işleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Servis Taşımacılığı Hizmeti</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H6" s="6">
-        <f>G6*0.20</f>
-        <v/>
-      </c>
-      <c r="I6" s="6">
-        <f>H6*F6</f>
-        <v/>
-      </c>
-      <c r="J6" s="6">
-        <f>H6-I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>FTR2026004</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Ege Gıda Dağıtım</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Temizlik Hizmeti</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H7" s="6">
-        <f>G7*0.20</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>H7*F7</f>
-        <v/>
-      </c>
-      <c r="J7" s="6">
-        <f>H7-I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>FTR2026005</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Akdeniz Otomotiv</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Özel Güvenlik Hizmeti</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>60000</v>
-      </c>
-      <c r="H8" s="6">
-        <f>G8*0.20</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>H8*F8</f>
-        <v/>
-      </c>
-      <c r="J8" s="6">
-        <f>H8-I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>TOPLAMLAR</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="8">
-        <f>SUM(G4:G8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="8">
-        <f>SUM(H4:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="8">
-        <f>SUM(I4:I8)</f>
-        <v/>
-      </c>
-      <c r="J9" s="8">
-        <f>SUM(J4:J8)</f>
-        <v/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Personel ve öğrenci servis taşımacılığı işleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Her Türlü Yük Taşımacılığı Hizmeti</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Karayolu, denizyolu ve havayolu ile yük ve kargo taşıma hizmetleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Her Türlü Baskı ve Basım Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Matbaacılık, broşür, katalog, ambalaj baskı ve ciltleme işleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Ticari Reklam Hizmetleri</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Dijital, televizyon, gazete veya billboard reklam yayınlama ve tasarım hizmetleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Diğer Hizmetler (Kapsam İçi Kurumlarca Alınan)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Belirlenmiş alıcı kurum ve kuruluşlara ifa edilen diğer genel hizmetler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Hurda ve Atık Teslimleri (Metal, Plastik, Kağıt, Cam)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>KDV Kanunu 17/4-g istisnasından vazgeçenlerin hurda teslimleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Pamuk, Tiftik, Yün ve Yapağı ile Ham Post ve Deri Teslimleri</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Tekstil ve deri sanayii ham madde teslimleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Ağaç ve Orman Ürünleri Teslimi (Tomruk, Kereste, Talaş)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Orman ürünleri, tomruk, odun ve kereste teslimleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Demir-Çelik Ürünlerinin Teslimi</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>İnşaat demiri, çubuk, profil ve çelik levha teslimleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bakır, Çinko, Alüminyum ve Kurşun Ürünlerinin Teslimi</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>İlk üreticilerden veya tüccarlardan alınan demir dışı metal mamulleri.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
